--- a/data/trans_bre/MCS12_SP_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R2-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 20,08</t>
+          <t>2,44; 19,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 26,81</t>
+          <t>10,45; 26,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 18,73</t>
+          <t>2,71; 19,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 9,93</t>
+          <t>-6,16; 10,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 56,17</t>
+          <t>5,14; 51,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,29; 51,47</t>
+          <t>17,16; 52,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 35,64</t>
+          <t>4,4; 37,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 35,33</t>
+          <t>-16,08; 34,55</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 19,19</t>
+          <t>6,18; 18,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 22,22</t>
+          <t>10,38; 22,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 13,37</t>
+          <t>2,23; 12,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 16,52</t>
+          <t>4,06; 16,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,23; 36,62</t>
+          <t>10,45; 36,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,14; 99,93</t>
+          <t>36,0; 100,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,31; 72,82</t>
+          <t>11,73; 72,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,28; 70,9</t>
+          <t>13,44; 70,27</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 21,12</t>
+          <t>6,07; 20,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 24,53</t>
+          <t>9,81; 24,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 20,53</t>
+          <t>4,62; 19,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 17,67</t>
+          <t>4,19; 17,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,31; 91,71</t>
+          <t>20,25; 89,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,62; 55,33</t>
+          <t>18,75; 56,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 47,48</t>
+          <t>8,61; 44,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,77; 75,65</t>
+          <t>13,68; 74,49</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 15,85</t>
+          <t>1,57; 15,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 17,54</t>
+          <t>3,86; 17,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 17,16</t>
+          <t>2,58; 17,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 36,26</t>
+          <t>1,47; 35,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 41,92</t>
+          <t>3,47; 39,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 28,99</t>
+          <t>5,83; 28,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 42,13</t>
+          <t>5,61; 44,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 131,09</t>
+          <t>3,5; 129,23</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 21,64</t>
+          <t>2,07; 22,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 22,86</t>
+          <t>4,23; 22,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 7,99</t>
+          <t>-4,93; 7,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 14,17</t>
+          <t>0,26; 14,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 49,17</t>
+          <t>3,68; 52,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 73,29</t>
+          <t>9,49; 71,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 9,69</t>
+          <t>-5,45; 8,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 19,96</t>
+          <t>0,33; 20,23</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,33; 21,18</t>
+          <t>4,58; 20,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 17,74</t>
+          <t>0,11; 17,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 18,86</t>
+          <t>1,91; 18,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 10,11</t>
+          <t>-3,45; 11,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,28; 70,31</t>
+          <t>11,03; 69,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 36,24</t>
+          <t>0,11; 36,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 62,98</t>
+          <t>4,76; 60,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 33,58</t>
+          <t>-9,21; 35,8</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,09; 19,59</t>
+          <t>7,65; 19,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,29; 15,54</t>
+          <t>4,47; 15,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 10,71</t>
+          <t>-1,77; 9,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,78; 38,28</t>
+          <t>8,82; 36,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,44; 60,96</t>
+          <t>20,29; 59,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 29,92</t>
+          <t>7,5; 29,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 21,4</t>
+          <t>-2,94; 20,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,02; 79,08</t>
+          <t>16,39; 73,06</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,71; 11,86</t>
+          <t>1,68; 11,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,25; 16,51</t>
+          <t>6,6; 16,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,43</t>
+          <t>-1,98; 8,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,37; 46,35</t>
+          <t>7,42; 43,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,7; 24,62</t>
+          <t>3,16; 24,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,73; 35,28</t>
+          <t>12,43; 34,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 14,43</t>
+          <t>-3,48; 16,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,11; 309,9</t>
+          <t>14,29; 217,58</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,46; 13,38</t>
+          <t>8,51; 13,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,29</t>
+          <t>10,49; 15,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,38</t>
+          <t>4,39; 9,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,41; 24,88</t>
+          <t>9,23; 26,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,96; 32,03</t>
+          <t>19,18; 32,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,82; 32,26</t>
+          <t>20,81; 31,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,64; 20,07</t>
+          <t>8,93; 19,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22,65; 74,33</t>
+          <t>22,49; 83,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/MCS12_SP_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 19,53</t>
+          <t>2,35; 19,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 26,42</t>
+          <t>10,7; 26,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 19,57</t>
+          <t>2,89; 19,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 10,08</t>
+          <t>-5,29; 7,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 51,91</t>
+          <t>4,71; 53,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 52,18</t>
+          <t>18,08; 52,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 37,62</t>
+          <t>5,58; 37,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 34,55</t>
+          <t>-13,89; 27,34</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,21</t>
+          <t>9,77</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 18,9</t>
+          <t>6,72; 18,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,38; 22,13</t>
+          <t>9,23; 21,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 12,85</t>
+          <t>2,58; 13,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 16,16</t>
+          <t>4,03; 15,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,45; 36,48</t>
+          <t>11,22; 35,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,0; 100,0</t>
+          <t>32,72; 100,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 72,49</t>
+          <t>10,74; 74,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,44; 70,27</t>
+          <t>12,59; 62,97</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,02</t>
+          <t>10,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 20,23</t>
+          <t>6,48; 21,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 24,85</t>
+          <t>9,69; 24,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 19,62</t>
+          <t>5,58; 19,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 17,57</t>
+          <t>3,37; 16,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,25; 89,25</t>
+          <t>21,43; 91,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,75; 56,17</t>
+          <t>18,5; 53,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 44,91</t>
+          <t>9,81; 43,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 74,49</t>
+          <t>10,39; 69,5</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,53</t>
+          <t>9,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 15,21</t>
+          <t>1,23; 15,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 17,36</t>
+          <t>3,41; 17,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 17,83</t>
+          <t>2,66; 17,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 35,88</t>
+          <t>1,74; 17,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 39,89</t>
+          <t>2,17; 40,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 28,97</t>
+          <t>4,88; 29,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 44,9</t>
+          <t>5,38; 43,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 129,23</t>
+          <t>4,5; 62,22</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>8,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 22,31</t>
+          <t>2,37; 21,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 22,67</t>
+          <t>4,55; 23,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 7,23</t>
+          <t>-5,23; 7,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 14,48</t>
+          <t>1,54; 15,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 52,36</t>
+          <t>4,79; 52,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 71,27</t>
+          <t>11,06; 73,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 8,61</t>
+          <t>-5,97; 9,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 20,23</t>
+          <t>2,14; 21,84</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 20,86</t>
+          <t>3,36; 20,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 17,89</t>
+          <t>0,87; 17,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,91; 18,84</t>
+          <t>2,68; 19,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 11,07</t>
+          <t>-2,87; 10,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,03; 69,89</t>
+          <t>8,68; 68,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 36,5</t>
+          <t>1,39; 35,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 60,93</t>
+          <t>6,7; 64,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 35,8</t>
+          <t>-7,89; 35,4</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>11,8</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,65; 19,49</t>
+          <t>7,57; 18,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 15,49</t>
+          <t>4,03; 15,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 9,87</t>
+          <t>-0,77; 10,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,82; 36,45</t>
+          <t>5,9; 17,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,29; 59,63</t>
+          <t>19,97; 57,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 29,65</t>
+          <t>6,95; 30,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 20,24</t>
+          <t>-1,43; 20,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,39; 73,06</t>
+          <t>11,1; 36,04</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,43</t>
+          <t>9,25</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 11,72</t>
+          <t>1,28; 11,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,6; 16,47</t>
+          <t>6,42; 16,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 8,28</t>
+          <t>-2,56; 7,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 43,18</t>
+          <t>4,16; 14,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,16; 24,24</t>
+          <t>2,4; 23,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,43; 34,86</t>
+          <t>12,08; 34,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 16,05</t>
+          <t>-4,51; 14,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,29; 217,58</t>
+          <t>7,95; 30,82</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15,17</t>
+          <t>8,92</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,51</t>
+          <t>8,38; 13,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,49; 15,17</t>
+          <t>10,48; 15,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,14</t>
+          <t>4,07; 8,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,23; 26,71</t>
+          <t>6,68; 10,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,18; 32,16</t>
+          <t>18,68; 32,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,81; 31,85</t>
+          <t>20,88; 32,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,93; 19,45</t>
+          <t>8,33; 19,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22,49; 83,69</t>
+          <t>15,39; 27,09</t>
         </is>
       </c>
     </row>
